--- a/Exam/gymtrackerpro/lib/schema/__tests__/wbt/utils/e164PhoneRegexWbt-wbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/wbt/utils/e164PhoneRegexWbt-wbt-form.xlsx
@@ -202,7 +202,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-17</t>
+    <t>SCHEMA-19</t>
   </si>
   <si>
     <t>100%</t>
